--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0002T0006Z000C1N4_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0002T0006Z000C1N4_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.69967655473119</v>
+        <v>5.801197440143818</v>
       </c>
       <c r="D2" t="n">
-        <v>35.91743529978997</v>
+        <v>5.836583236215871</v>
       </c>
       <c r="E2" t="n">
-        <v>2.730689208670997</v>
+        <v>0.4437369964090369</v>
       </c>
       <c r="F2" t="n">
-        <v>2.935700397942911</v>
+        <v>0.4770513146657232</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>31.69292370060785</v>
+        <v>5.150100101348776</v>
       </c>
       <c r="D3" t="n">
-        <v>31.54669095327201</v>
+        <v>5.126337279906702</v>
       </c>
       <c r="E3" t="n">
-        <v>2.730689208670997</v>
+        <v>0.4437369964090369</v>
       </c>
       <c r="F3" t="n">
-        <v>2.935700397942911</v>
+        <v>0.4770513146657232</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>34.98613841237864</v>
+        <v>5.68524749201153</v>
       </c>
       <c r="D4" t="n">
-        <v>35.2558814434285</v>
+        <v>5.729080734557131</v>
       </c>
       <c r="E4" t="n">
-        <v>2.730689208670997</v>
+        <v>0.4437369964090369</v>
       </c>
       <c r="F4" t="n">
-        <v>2.935700397942911</v>
+        <v>0.4770513146657232</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.47958053331114</v>
+        <v>5.440431836663061</v>
       </c>
       <c r="D5" t="n">
-        <v>33.71934604206385</v>
+        <v>5.479393731835376</v>
       </c>
       <c r="E5" t="n">
-        <v>2.730689208670997</v>
+        <v>0.4437369964090369</v>
       </c>
       <c r="F5" t="n">
-        <v>2.935700397942911</v>
+        <v>0.4770513146657232</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.06611291233167</v>
+        <v>4.560743348253896</v>
       </c>
       <c r="D6" t="n">
-        <v>27.80620319300867</v>
+        <v>4.518508018863908</v>
       </c>
       <c r="E6" t="n">
-        <v>2.730689208670997</v>
+        <v>0.4437369964090369</v>
       </c>
       <c r="F6" t="n">
-        <v>2.935700397942911</v>
+        <v>0.4770513146657232</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
